--- a/TEMPLATE_DATA FOR DASHBOARD.xlsx
+++ b/TEMPLATE_DATA FOR DASHBOARD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nykgroup-my.sharepoint.com/personal/thuhuong_ngo_nykgroup_com/Documents/THU HUONG_DAILY JOB/MULTI-DATA/PROJECT OF YLK/To be advised (unification)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1A28C55-8130-4BC9-9DCF-9219BD06BA04}"/>
+  <xr:revisionPtr revIDLastSave="611" documentId="8_{F9537D5D-B12A-4A4C-AF40-128E8D45C306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22754722-E463-41A9-80A9-5672218791D1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="745" xr2:uid="{E21F554E-3F05-4DDC-8BE4-80952248A30F}"/>
   </bookViews>
   <sheets>
     <sheet name="HC" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,12 @@
     <sheet name="BU allocation" sheetId="5" r:id="rId3"/>
     <sheet name="N-S Customer list" sheetId="6" r:id="rId4"/>
     <sheet name="HAN Customer list" sheetId="8" r:id="rId5"/>
-    <sheet name="HLC" sheetId="9" r:id="rId6"/>
+    <sheet name="HLC Customer list" sheetId="9" r:id="rId6"/>
+    <sheet name="CS FTE" sheetId="10" r:id="rId7"/>
+    <sheet name="C" sheetId="11" r:id="rId8"/>
+    <sheet name="A" sheetId="12" r:id="rId9"/>
+    <sheet name="S" sheetId="13" r:id="rId10"/>
+    <sheet name="E" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="301">
   <si>
     <t>Approved HC</t>
   </si>
@@ -557,19 +562,410 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>CS PIC</t>
+  </si>
+  <si>
+    <t>BTD</t>
+  </si>
+  <si>
+    <t>BHT</t>
+  </si>
+  <si>
+    <t>NTH</t>
+  </si>
+  <si>
+    <t>NLC</t>
+  </si>
+  <si>
+    <t>DTL</t>
+  </si>
+  <si>
+    <t>NBN</t>
+  </si>
+  <si>
+    <t>TTL</t>
+  </si>
+  <si>
+    <t>THT</t>
+  </si>
+  <si>
+    <t>HTT</t>
+  </si>
+  <si>
+    <t>FTE PER CSPIC</t>
+  </si>
+  <si>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>AE-ABBB</t>
+  </si>
+  <si>
+    <t>AE-CBBB</t>
+  </si>
+  <si>
+    <t>AE-CTAB</t>
+  </si>
+  <si>
+    <t>AE-CTAW</t>
+  </si>
+  <si>
+    <t>AE-CTBB</t>
+  </si>
+  <si>
+    <t>AE-CTWB</t>
+  </si>
+  <si>
+    <t>AE-TABB</t>
+  </si>
+  <si>
+    <t>AE-TBBB</t>
+  </si>
+  <si>
+    <t>AI-ABBB</t>
+  </si>
+  <si>
+    <t>AI-CABB</t>
+  </si>
+  <si>
+    <t>AI-CBBB</t>
+  </si>
+  <si>
+    <t>AI-CGBB</t>
+  </si>
+  <si>
+    <t>AI-CTAB</t>
+  </si>
+  <si>
+    <t>AI-CTBB</t>
+  </si>
+  <si>
+    <t>AI-CTGB</t>
+  </si>
+  <si>
+    <t>AI-CTWB</t>
+  </si>
+  <si>
+    <t>AI-CWBB</t>
+  </si>
+  <si>
+    <t>CE-CBTB</t>
+  </si>
+  <si>
+    <t>CE-CBTC</t>
+  </si>
+  <si>
+    <t>CE-CBTW</t>
+  </si>
+  <si>
+    <t>CI-CBBB</t>
+  </si>
+  <si>
+    <t>CI-CWBB</t>
+  </si>
+  <si>
+    <t>DE-CBBB</t>
+  </si>
+  <si>
+    <t>DE-CGBB</t>
+  </si>
+  <si>
+    <t>DE-CTBB</t>
+  </si>
+  <si>
+    <t>DE-CTGB</t>
+  </si>
+  <si>
+    <t>DE-CTWB</t>
+  </si>
+  <si>
+    <t>DE-TATC</t>
+  </si>
+  <si>
+    <t>DE-TBBB</t>
+  </si>
+  <si>
+    <t>DE-TGBB</t>
+  </si>
+  <si>
+    <t>DE-TWBB</t>
+  </si>
+  <si>
+    <t>DI-CBBB</t>
+  </si>
+  <si>
+    <t>DI-CTBB</t>
+  </si>
+  <si>
+    <t>DI-CTGB</t>
+  </si>
+  <si>
+    <t>DI-CTWB</t>
+  </si>
+  <si>
+    <t>DI-GBBB</t>
+  </si>
+  <si>
+    <t>DI-TGBB</t>
+  </si>
+  <si>
+    <t>DI-TWBB</t>
+  </si>
+  <si>
+    <t>DM-CBBB</t>
+  </si>
+  <si>
+    <t>DM-CGBB</t>
+  </si>
+  <si>
+    <t>DM-TBBB</t>
+  </si>
+  <si>
+    <t>DM-TOTB</t>
+  </si>
+  <si>
+    <t>OEFCL-CBBB</t>
+  </si>
+  <si>
+    <t>OEFCL-CTBB</t>
+  </si>
+  <si>
+    <t>OEFCL-CTOB</t>
+  </si>
+  <si>
+    <t>OEFCL-CTWB</t>
+  </si>
+  <si>
+    <t>OEFCL-FCTB</t>
+  </si>
+  <si>
+    <t>OEFCL-OBBB</t>
+  </si>
+  <si>
+    <t>OEFCL-TBBB</t>
+  </si>
+  <si>
+    <t>OEFCL-TOBB</t>
+  </si>
+  <si>
+    <t>OELCL-CBBB</t>
+  </si>
+  <si>
+    <t>OELCL-CTBB</t>
+  </si>
+  <si>
+    <t>OELCL-CTGB</t>
+  </si>
+  <si>
+    <t>OELCL-CTOB</t>
+  </si>
+  <si>
+    <t>OELCL-CTWB</t>
+  </si>
+  <si>
+    <t>OELCL-OBBB</t>
+  </si>
+  <si>
+    <t>OELCL-TBBB</t>
+  </si>
+  <si>
+    <t>OELCL-TOBB</t>
+  </si>
+  <si>
+    <t>OIFCL-CTBB</t>
+  </si>
+  <si>
+    <t>OIFCL-CTGB</t>
+  </si>
+  <si>
+    <t>OIFCL-CTOB</t>
+  </si>
+  <si>
+    <t>OIFCL-CTOW</t>
+  </si>
+  <si>
+    <t>OIFCL-CTWB</t>
+  </si>
+  <si>
+    <t>OIFCL-CWBB</t>
+  </si>
+  <si>
+    <t>OIFCL-OBBB</t>
+  </si>
+  <si>
+    <t>OIFCL-TBBB</t>
+  </si>
+  <si>
+    <t>OILCL-CBBB</t>
+  </si>
+  <si>
+    <t>OILCL-CTBB</t>
+  </si>
+  <si>
+    <t>OILCL-CTGB</t>
+  </si>
+  <si>
+    <t>OILCL-CTOB</t>
+  </si>
+  <si>
+    <t>OILCL-CTWB</t>
+  </si>
+  <si>
+    <t>OILCL-CWBB</t>
+  </si>
+  <si>
+    <t>OILCL-OBBB</t>
+  </si>
+  <si>
+    <t>CCCO</t>
+  </si>
+  <si>
+    <t>TRFU</t>
+  </si>
+  <si>
+    <t>CCLS</t>
+  </si>
+  <si>
+    <t>CSIN</t>
+  </si>
+  <si>
+    <t>TRLA</t>
+  </si>
+  <si>
+    <t>TRHI</t>
+  </si>
+  <si>
+    <t>TRHE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancillary Service </t>
+  </si>
+  <si>
+    <t>Suppoting Activity</t>
+  </si>
+  <si>
+    <t>AE-AFOS</t>
+  </si>
+  <si>
+    <t>AI-AFOS</t>
+  </si>
+  <si>
+    <t>AE-OCDN</t>
+  </si>
+  <si>
+    <t>AI-OCDN</t>
+  </si>
+  <si>
+    <t>CCLD</t>
+  </si>
+  <si>
+    <t>TRMD</t>
+  </si>
+  <si>
+    <t>CSBK</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>KD</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>AE-CSMF</t>
+  </si>
+  <si>
+    <t>AI-CSMF</t>
+  </si>
+  <si>
+    <t>OE-CSMF</t>
+  </si>
+  <si>
+    <t>OI-CSMF</t>
+  </si>
+  <si>
+    <t>Exception Handling</t>
+  </si>
+  <si>
+    <t>SYSI</t>
+  </si>
+  <si>
+    <t>CDEC</t>
+  </si>
+  <si>
+    <t>CDMG</t>
+  </si>
+  <si>
+    <t>SCHG</t>
+  </si>
+  <si>
+    <t>CAPS</t>
+  </si>
+  <si>
+    <t>DOCD</t>
+  </si>
+  <si>
+    <t>EXCEPTION DETAIL</t>
+  </si>
+  <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>VNACCS failure</t>
+  </si>
+  <si>
+    <t>Wrong CDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrong/lack of Shipping Doc </t>
+  </si>
+  <si>
+    <t>Trouble shooting</t>
+  </si>
+  <si>
+    <t>Vessel/Flight delay/skip/change vessel/schedule</t>
+  </si>
+  <si>
+    <t>Cargo damage (all types)</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Core Service</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00;\-#,##0.00;\-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,8 +1038,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,8 +1070,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -763,6 +1178,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -772,7 +1215,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -869,14 +1312,22 @@
     <xf numFmtId="166" fontId="5" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -884,8 +1335,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -893,26 +1350,61 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -923,7 +1415,48 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="標準_1問題1シートBlank" xfId="4" xr:uid="{A683D387-F1ED-42C3-928D-68831043DFA8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1262,66 +1795,66 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46" t="s">
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="52" t="s">
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="M2" s="53"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="47" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="47" t="s">
+      <c r="I3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="48" t="s">
+      <c r="J3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="48" t="s">
+      <c r="L3" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="M3" s="54" t="s">
+      <c r="M3" s="41" t="s">
         <v>170</v>
       </c>
     </row>
@@ -1597,7 +2130,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="51">
+      <c r="E15" s="40">
         <f>L17</f>
         <v>0.99090909090909096</v>
       </c>
@@ -1693,7 +2226,7 @@
         <f>J17+I17</f>
         <v>21.8</v>
       </c>
-      <c r="L17" s="50">
+      <c r="L17" s="24">
         <f>K17/H17</f>
         <v>0.99090909090909096</v>
       </c>
@@ -1718,7 +2251,7 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
-      <c r="L18" s="51"/>
+      <c r="L18" s="40"/>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
@@ -1925,7 +2458,7 @@
       <c r="J28" s="37">
         <v>17.5</v>
       </c>
-      <c r="K28" s="49">
+      <c r="K28" s="39">
         <f>J28+I28</f>
         <v>18.5</v>
       </c>
@@ -1971,7 +2504,7 @@
       <c r="J29" s="4">
         <v>17.8</v>
       </c>
-      <c r="K29" s="49">
+      <c r="K29" s="39">
         <f>J29+I29</f>
         <v>18.8</v>
       </c>
@@ -2412,6 +2945,663 @@
     <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A25CF0A-A464-4B26-B6F8-178B29BE8BAF}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="48"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="2">
+        <v>54</v>
+      </c>
+      <c r="D5" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="62">
+        <v>73</v>
+      </c>
+      <c r="D6" s="62">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="63">
+        <v>289</v>
+      </c>
+      <c r="D7" s="63">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="2">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="2">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="2">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1166</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="2">
+        <v>129</v>
+      </c>
+      <c r="D12" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C13" s="2">
+        <v>7</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="2">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B4:B5">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14:B17">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBCC9D14-69F0-4B23-94C0-2C21A38E047A}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="89.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="67"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" customHeight="1">
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="2">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A7" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A8" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="2">
+        <f>59+4</f>
+        <v>63</v>
+      </c>
+      <c r="G8" s="2">
+        <f>59+4</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A9" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="2">
+        <v>19</v>
+      </c>
+      <c r="G11" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A12" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F12" s="2">
+        <v>47</v>
+      </c>
+      <c r="G12" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A13" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A14" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A17" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A18" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A19" s="31"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+    </row>
+    <row r="20" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A20" s="31"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+    </row>
+    <row r="21" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A21" s="31"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+    </row>
+    <row r="22" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A22" s="31"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+    </row>
+    <row r="23" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A23" s="31"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+    </row>
+    <row r="24" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A24" s="31"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+    </row>
+    <row r="25" spans="1:7" ht="26.25" customHeight="1">
+      <c r="A25" s="31"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2436,39 +3626,39 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="24" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="43"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="44"/>
       <c r="D3" s="5" t="s">
         <v>25</v>
       </c>
@@ -4079,46 +5269,46 @@
       <c r="A1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="48"/>
+      <c r="F2" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40" t="s">
+      <c r="G2" s="48"/>
+      <c r="H2" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40" t="s">
+      <c r="I2" s="48"/>
+      <c r="J2" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="38" t="s">
+      <c r="K2" s="48"/>
+      <c r="L2" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="47" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
       <c r="D3" s="9" t="s">
         <v>50</v>
       </c>
@@ -4143,8 +5333,8 @@
       <c r="K3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
@@ -5323,16 +6513,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5347,35 +6537,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="38"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="38"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="29" t="s">
         <v>52</v>
       </c>
@@ -8496,22 +9686,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="29" t="s">
         <v>52</v>
       </c>
@@ -9516,22 +10706,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="29" t="s">
         <v>52</v>
       </c>
@@ -10525,4 +11715,1373 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E418FAC-AA78-41C0-9BF4-0D3B9752C4B5}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="55">
+        <v>0.81541193181818172</v>
+      </c>
+      <c r="D3" s="53">
+        <v>0.79455492424242424</v>
+      </c>
+      <c r="E3" s="53">
+        <v>0.9034801136363636</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0.78721590909090911</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="55">
+        <v>1.0926294191919204</v>
+      </c>
+      <c r="D4" s="53">
+        <v>1.0602982954545466</v>
+      </c>
+      <c r="E4" s="53">
+        <v>1.0719854797979811</v>
+      </c>
+      <c r="F4" s="53">
+        <v>1.0687815656565662</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="55">
+        <v>0.95951704545454541</v>
+      </c>
+      <c r="D5" s="53">
+        <v>1.034375</v>
+      </c>
+      <c r="E5" s="53">
+        <v>1.1954703282828283</v>
+      </c>
+      <c r="F5" s="53">
+        <v>1.353811553030303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="55">
+        <v>0.78371212121212119</v>
+      </c>
+      <c r="D6" s="53">
+        <v>0.79348169191919193</v>
+      </c>
+      <c r="E6" s="53">
+        <v>0.81051925505050493</v>
+      </c>
+      <c r="F6" s="53">
+        <v>0.74292140151515151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="55">
+        <v>1.681344696969697</v>
+      </c>
+      <c r="D7" s="53">
+        <v>1.556155303030303</v>
+      </c>
+      <c r="E7" s="53">
+        <v>1.8897253787878787</v>
+      </c>
+      <c r="F7" s="53">
+        <v>2.1298532196969697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="55">
+        <v>0.95852272727272725</v>
+      </c>
+      <c r="D8" s="53">
+        <v>1.0760179924242423</v>
+      </c>
+      <c r="E8" s="53">
+        <v>0.9447916666666667</v>
+      </c>
+      <c r="F8" s="53">
+        <v>1.1360085227272727</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="55">
+        <v>1.5947127525252518</v>
+      </c>
+      <c r="D9" s="53">
+        <v>1.4549558080808076</v>
+      </c>
+      <c r="E9" s="53">
+        <v>1.8606613005050507</v>
+      </c>
+      <c r="F9" s="53">
+        <v>1.3066998106060597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="55">
+        <v>0.97215909090909092</v>
+      </c>
+      <c r="D10" s="53">
+        <v>0.95999053030303039</v>
+      </c>
+      <c r="E10" s="53">
+        <v>1.0148200757575756</v>
+      </c>
+      <c r="F10" s="53">
+        <v>1.036813446969697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="55">
+        <v>1.3566287878787879</v>
+      </c>
+      <c r="D11" s="53">
+        <v>1.3369318181818182</v>
+      </c>
+      <c r="E11" s="53">
+        <v>1.470785984848485</v>
+      </c>
+      <c r="F11" s="53">
+        <v>1.5597064393939393</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AC7A06-A2E4-4CC8-9045-1D086ED83B34}">
+  <dimension ref="A1:D76"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="57"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="4">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="4">
+        <v>54</v>
+      </c>
+      <c r="D5" s="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="4">
+        <v>193</v>
+      </c>
+      <c r="D6" s="4">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="4">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="4">
+        <v>70</v>
+      </c>
+      <c r="D10" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="4">
+        <v>113</v>
+      </c>
+      <c r="D12" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="4">
+        <v>166</v>
+      </c>
+      <c r="D14" s="4">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="4">
+        <v>162</v>
+      </c>
+      <c r="D16" s="4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" s="4">
+        <v>195</v>
+      </c>
+      <c r="D17" s="4">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="4">
+        <v>15</v>
+      </c>
+      <c r="D18" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="4">
+        <v>4</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="4">
+        <v>8</v>
+      </c>
+      <c r="D24" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C25" s="4">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="4">
+        <v>127</v>
+      </c>
+      <c r="D26" s="4">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="56" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="4">
+        <v>19</v>
+      </c>
+      <c r="D28" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="4">
+        <v>18</v>
+      </c>
+      <c r="D30" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C32" s="4">
+        <v>61</v>
+      </c>
+      <c r="D32" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="4">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="56" t="s">
+        <v>215</v>
+      </c>
+      <c r="C35" s="4">
+        <v>188</v>
+      </c>
+      <c r="D35" s="4">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="4">
+        <v>30</v>
+      </c>
+      <c r="D36" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="C41" s="4">
+        <v>37</v>
+      </c>
+      <c r="D41" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C42" s="4">
+        <v>4</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="56" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" s="4">
+        <v>19</v>
+      </c>
+      <c r="D44" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="4">
+        <v>63</v>
+      </c>
+      <c r="D47" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" s="4">
+        <v>23</v>
+      </c>
+      <c r="D48" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="4">
+        <v>2</v>
+      </c>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="4">
+        <v>48</v>
+      </c>
+      <c r="D50" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="56" t="s">
+        <v>231</v>
+      </c>
+      <c r="C51" s="4">
+        <v>8</v>
+      </c>
+      <c r="D51" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" s="56" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="4">
+        <v>41</v>
+      </c>
+      <c r="D53" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="4">
+        <v>6</v>
+      </c>
+      <c r="D54" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="56" t="s">
+        <v>235</v>
+      </c>
+      <c r="C55" s="4">
+        <v>74</v>
+      </c>
+      <c r="D55" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="4">
+        <v>14</v>
+      </c>
+      <c r="D57" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>238</v>
+      </c>
+      <c r="C58" s="4">
+        <v>3</v>
+      </c>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C59" s="4">
+        <v>34</v>
+      </c>
+      <c r="D59" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="56" t="s">
+        <v>240</v>
+      </c>
+      <c r="C60" s="4">
+        <v>50</v>
+      </c>
+      <c r="D60" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" s="4">
+        <v>106</v>
+      </c>
+      <c r="D61" s="4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="C62" s="4">
+        <v>52</v>
+      </c>
+      <c r="D62" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="C63" s="4">
+        <v>4</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="C64" s="4">
+        <v>38</v>
+      </c>
+      <c r="D64" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="C65" s="4">
+        <v>1</v>
+      </c>
+      <c r="D65" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="C66" s="4">
+        <v>24</v>
+      </c>
+      <c r="D66" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="C67" s="4">
+        <v>4</v>
+      </c>
+      <c r="D67" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="C68" s="4">
+        <v>43</v>
+      </c>
+      <c r="D68" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" s="4">
+        <v>5</v>
+      </c>
+      <c r="D69" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B70" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="C70" s="4">
+        <v>10</v>
+      </c>
+      <c r="D70" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="C71" s="4">
+        <v>42</v>
+      </c>
+      <c r="D71" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" s="4">
+        <v>23</v>
+      </c>
+      <c r="D72" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C73" s="4">
+        <v>19</v>
+      </c>
+      <c r="D73" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="C74" s="4">
+        <v>5</v>
+      </c>
+      <c r="D74" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="C76" s="4">
+        <v>31</v>
+      </c>
+      <c r="D76" s="4">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2355767F-9FD0-48C9-95BA-7FAE68492F91}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="65"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4" s="2">
+        <v>63</v>
+      </c>
+      <c r="D4" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B4:B10">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>